--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pemphero\Desktop\Transcript_email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BEAE1C-921D-4F87-BBFA-8489E935A7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A8D7D1-BAD3-4842-827E-79E5B3D753DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="15375" windowHeight="8265" xr2:uid="{BA537141-6C0F-42B0-80AF-0F5688DAAD6D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BA537141-6C0F-42B0-80AF-0F5688DAAD6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,15 +42,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>Jane Smith</t>
-  </si>
-  <si>
-    <t>Bob Johnson</t>
-  </si>
-  <si>
     <t>mandindip@mchs.adventist.org</t>
   </si>
   <si>
@@ -94,6 +85,15 @@
   </si>
   <si>
     <t>2 Years</t>
+  </si>
+  <si>
+    <t>Blessings Chirwa</t>
+  </si>
+  <si>
+    <t>Pemphero Mandindi</t>
+  </si>
+  <si>
+    <t>Raphael Chirwa</t>
   </si>
 </sst>
 </file>
@@ -503,7 +503,7 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -519,53 +519,53 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F2" s="4">
         <v>46266</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4">
         <v>46266</v>
@@ -573,19 +573,19 @@
     </row>
     <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F4" s="4">
         <v>46280</v>
